--- a/tabular/build/locus/lineage-mapping/herv_locus_mapping_by_classification.xlsx
+++ b/tabular/build/locus/lineage-mapping/herv_locus_mapping_by_classification.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/build/locus/lineage-mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80ED8025-1CBF-294C-90DE-7075B4A6F6C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{C4B10D42-1CE4-4343-A9B2-3167C42EF485}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27480" windowHeight="16940"/>
   </bookViews>
@@ -408,7 +408,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,6 +586,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8AD8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -749,8 +755,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -798,6 +805,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF8AD8"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1223,7 +1235,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11">
